--- a/data/trans_camb/P57_AC_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P57_AC_R-Estudios-trans_camb.xlsx
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,7; 0,5</t>
+          <t>-7,85; 0,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,74; 9,06</t>
+          <t>0,83; 8,97</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-12,95; -3,32</t>
+          <t>-13,13; -3,49</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 1,29</t>
+          <t>-5,38; 1,04</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,78; 10,04</t>
+          <t>3,99; 10,25</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,84; -4,67</t>
+          <t>-11,57; -4,76</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,12; -0,13</t>
+          <t>-5,1; 0,14</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,41; 8,54</t>
+          <t>3,77; 8,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,92; -5,28</t>
+          <t>-10,62; -5,2</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,05; 0,76</t>
+          <t>-10,43; 0,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,02; 12,48</t>
+          <t>1,06; 12,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-17,08; -4,49</t>
+          <t>-17,51; -4,84</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 1,69</t>
+          <t>-6,81; 1,36</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,73; 13,16</t>
+          <t>5,06; 13,56</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,96; -6,13</t>
+          <t>-14,56; -6,24</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,53; -0,07</t>
+          <t>-6,65; 0,19</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,46; 11,39</t>
+          <t>4,86; 11,43</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-14,05; -7,01</t>
+          <t>-13,84; -6,89</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-3,14; 3,62</t>
+          <t>-2,76; 3,52</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,58; 18,61</t>
+          <t>12,95; 18,77</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-28,65; -2,71</t>
+          <t>-28,56; -2,72</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 9,57</t>
+          <t>3,05; 9,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,27; 19,01</t>
+          <t>13,23; 18,86</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-15,66; -3,17</t>
+          <t>-13,51; -2,91</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,95; 5,27</t>
+          <t>0,74; 5,29</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>13,83; 17,89</t>
+          <t>14,0; 18,04</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-19,36; -4,44</t>
+          <t>-19,23; -4,72</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,76; 5,83</t>
+          <t>-4,19; 5,57</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>18,75; 29,55</t>
+          <t>19,47; 30,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-43,45; -4,28</t>
+          <t>-44,26; -4,26</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>3,86; 14,71</t>
+          <t>4,64; 14,79</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,3; 29,36</t>
+          <t>19,14; 29,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,09; -4,73</t>
+          <t>-20,32; -4,5</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,43; 8,22</t>
+          <t>1,1; 8,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,6; 27,77</t>
+          <t>20,87; 28,02</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-29,38; -6,76</t>
+          <t>-29,37; -7,29</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,74; 2,8</t>
+          <t>-9,82; 2,47</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,37; 13,07</t>
+          <t>1,65; 12,55</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,77; -3,08</t>
+          <t>-14,01; -2,19</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-5,02; 9,02</t>
+          <t>-4,2; 8,58</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,41; 15,72</t>
+          <t>4,23; 15,99</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-12,77; -1,54</t>
+          <t>-13,83; -2,27</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,28; 3,77</t>
+          <t>-5,4; 3,63</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,79; 12,48</t>
+          <t>3,69; 12,07</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,6; -4,63</t>
+          <t>-12,43; -4,35</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,04; 4,31</t>
+          <t>-14,11; 3,93</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1,53; 20,45</t>
+          <t>2,41; 19,67</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-21,07; -4,89</t>
+          <t>-20,24; -3,46</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-7,61; 14,98</t>
+          <t>-6,4; 14,91</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,87; 26,93</t>
+          <t>6,45; 26,81</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-19,46; -2,31</t>
+          <t>-20,67; -3,91</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-7,96; 6,04</t>
+          <t>-8,06; 5,69</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,72; 20,02</t>
+          <t>5,59; 19,31</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-18,87; -7,39</t>
+          <t>-18,71; -6,98</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-4,1; 0,54</t>
+          <t>-3,86; 0,69</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,82; 13,32</t>
+          <t>8,79; 13,21</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-25,14; -6,03</t>
+          <t>-23,79; -5,93</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,1; 4,8</t>
+          <t>0,34; 4,62</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,23; 13,34</t>
+          <t>9,1; 13,41</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-13,68; -7,08</t>
+          <t>-14,12; -6,82</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,23; 2,04</t>
+          <t>-1,33; 2,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,73; 12,74</t>
+          <t>9,63; 12,65</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-18,41; -7,43</t>
+          <t>-17,5; -7,45</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,96; 0,81</t>
+          <t>-5,58; 1,04</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12,72; 20,01</t>
+          <t>12,65; 19,83</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-37,12; -8,92</t>
+          <t>-34,93; -8,81</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,25; 6,95</t>
+          <t>0,46; 6,57</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,84; 19,2</t>
+          <t>12,62; 19,26</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-19,26; -10,11</t>
+          <t>-20,08; -9,85</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,74; 2,96</t>
+          <t>-1,89; 3,11</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,89; 18,65</t>
+          <t>13,79; 18,52</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-26,7; -10,77</t>
+          <t>-25,06; -10,76</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P57_AC_R-Estudios-trans_camb.xlsx
+++ b/data/trans_camb/P57_AC_R-Estudios-trans_camb.xlsx
@@ -634,7 +634,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>-7,99</t>
+          <t>-7,96</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -649,7 +649,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>-8,21</t>
+          <t>-7,07</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -664,7 +664,7 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>-7,99</t>
+          <t>-7,34</t>
         </is>
       </c>
     </row>
@@ -677,47 +677,47 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-7,85; 0,33</t>
+          <t>-7,66; 0,31</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,83; 8,97</t>
+          <t>1,07; 8,86</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-13,13; -3,49</t>
+          <t>-12,67; -3,38</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-5,38; 1,04</t>
+          <t>-5,44; 1,68</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>3,99; 10,25</t>
+          <t>3,65; 10,34</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-11,57; -4,76</t>
+          <t>-10,66; -3,72</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-5,1; 0,14</t>
+          <t>-5,28; -0,04</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>3,77; 8,68</t>
+          <t>3,65; 8,57</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>-10,62; -5,2</t>
+          <t>-10,11; -4,43</t>
         </is>
       </c>
     </row>
@@ -740,7 +740,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>-10,78%</t>
+          <t>-10,74%</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -755,7 +755,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>-10,54%</t>
+          <t>-9,07%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
@@ -770,7 +770,7 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>-10,48%</t>
+          <t>-9,63%</t>
         </is>
       </c>
     </row>
@@ -783,47 +783,47 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-10,43; 0,44</t>
+          <t>-10,06; 0,44</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,06; 12,26</t>
+          <t>1,39; 12,26</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-17,51; -4,84</t>
+          <t>-16,98; -4,59</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 1,36</t>
+          <t>-6,85; 2,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>5,06; 13,56</t>
+          <t>4,59; 13,65</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-14,56; -6,24</t>
+          <t>-13,45; -4,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-6,65; 0,19</t>
+          <t>-6,84; -0,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>4,86; 11,43</t>
+          <t>4,71; 11,4</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>-13,84; -6,89</t>
+          <t>-13,07; -5,88</t>
         </is>
       </c>
     </row>
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>-10,31</t>
+          <t>-2,19</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -865,7 +865,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>-7,17</t>
+          <t>-3,13</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>-8,88</t>
+          <t>-2,63</t>
         </is>
       </c>
     </row>
@@ -893,47 +893,47 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-2,76; 3,52</t>
+          <t>-3,28; 3,49</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>12,95; 18,77</t>
+          <t>12,84; 18,69</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-28,56; -2,72</t>
+          <t>-5,23; 1,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,05; 9,63</t>
+          <t>2,9; 9,24</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,23; 18,86</t>
+          <t>12,84; 18,76</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-13,51; -2,91</t>
+          <t>-6,27; -0,14</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,74; 5,29</t>
+          <t>0,8; 5,44</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>14,0; 18,04</t>
+          <t>13,93; 17,9</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>-19,23; -4,72</t>
+          <t>-4,86; -0,09</t>
         </is>
       </c>
     </row>
@@ -956,7 +956,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>-15,96%</t>
+          <t>-3,38%</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -971,7 +971,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>-10,67%</t>
+          <t>-4,66%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>-13,48%</t>
+          <t>-3,99%</t>
         </is>
       </c>
     </row>
@@ -999,47 +999,47 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 5,57</t>
+          <t>-4,94; 5,61</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>19,47; 30,15</t>
+          <t>19,1; 29,74</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-44,26; -4,26</t>
+          <t>-7,93; 2,14</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,64; 14,79</t>
+          <t>4,27; 14,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>19,14; 29,07</t>
+          <t>18,6; 28,57</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-20,32; -4,5</t>
+          <t>-9,11; -0,25</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>1,1; 8,16</t>
+          <t>1,18; 8,44</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>20,87; 28,02</t>
+          <t>20,86; 27,89</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>-29,37; -7,29</t>
+          <t>-7,26; -0,14</t>
         </is>
       </c>
     </row>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>-8,56</t>
+          <t>-7,61</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>-8,03</t>
+          <t>-6,95</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>-8,47</t>
+          <t>-7,46</t>
         </is>
       </c>
     </row>
@@ -1109,47 +1109,47 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-9,82; 2,47</t>
+          <t>-9,75; 3,43</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,65; 12,55</t>
+          <t>1,19; 13,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-14,01; -2,19</t>
+          <t>-13,2; -1,69</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-4,2; 8,58</t>
+          <t>-4,46; 8,2</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,23; 15,99</t>
+          <t>4,28; 15,82</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-13,83; -2,27</t>
+          <t>-12,65; -1,47</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-5,4; 3,63</t>
+          <t>-5,62; 3,57</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>3,69; 12,07</t>
+          <t>4,09; 12,35</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>-12,43; -4,35</t>
+          <t>-11,66; -3,42</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>-12,81%</t>
+          <t>-11,38%</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>-12,83%</t>
+          <t>-11,1%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1202,7 +1202,7 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>-13,06%</t>
+          <t>-11,51%</t>
         </is>
       </c>
     </row>
@@ -1215,47 +1215,47 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>-14,11; 3,93</t>
+          <t>-14,05; 5,41</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2,41; 19,67</t>
+          <t>1,64; 19,89</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-20,24; -3,46</t>
+          <t>-19,1; -2,81</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-6,4; 14,91</t>
+          <t>-6,95; 13,76</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>6,45; 26,81</t>
+          <t>6,59; 26,99</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-20,67; -3,91</t>
+          <t>-19,01; -2,37</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>-8,06; 5,69</t>
+          <t>-8,52; 5,61</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5,59; 19,31</t>
+          <t>5,99; 19,69</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>-18,71; -6,98</t>
+          <t>-17,43; -5,46</t>
         </is>
       </c>
     </row>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>-11,18</t>
+          <t>-5,58</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -1297,7 +1297,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>-9,65</t>
+          <t>-6,85</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -1312,7 +1312,7 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>-10,44</t>
+          <t>-6,22</t>
         </is>
       </c>
     </row>
@@ -1325,47 +1325,47 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-3,86; 0,69</t>
+          <t>-3,78; 0,85</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>8,79; 13,21</t>
+          <t>9,04; 13,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-23,79; -5,93</t>
+          <t>-8,11; -3,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0,34; 4,62</t>
+          <t>0,31; 4,59</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>9,1; 13,41</t>
+          <t>9,28; 13,5</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-14,12; -6,82</t>
+          <t>-9,04; -4,68</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>-1,33; 2,11</t>
+          <t>-1,2; 2,11</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>9,63; 12,65</t>
+          <t>9,66; 12,61</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>-17,5; -7,45</t>
+          <t>-7,76; -4,54</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>-16,45%</t>
+          <t>-8,21%</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -1403,7 +1403,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>-13,64%</t>
+          <t>-9,68%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -1418,7 +1418,7 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>-15,05%</t>
+          <t>-8,96%</t>
         </is>
       </c>
     </row>
@@ -1431,47 +1431,47 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-5,58; 1,04</t>
+          <t>-5,47; 1,26</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>12,65; 19,83</t>
+          <t>13,1; 20,15</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-34,93; -8,81</t>
+          <t>-11,68; -4,63</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>0,46; 6,57</t>
+          <t>0,43; 6,6</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>12,62; 19,26</t>
+          <t>12,86; 19,45</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-20,08; -9,85</t>
+          <t>-12,63; -6,75</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 3,11</t>
+          <t>-1,73; 3,08</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>13,79; 18,52</t>
+          <t>13,75; 18,46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>-25,06; -10,76</t>
+          <t>-11,06; -6,59</t>
         </is>
       </c>
     </row>
